--- a/AAII_Financials/Quarterly/BABA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BABA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
   <si>
     <t>BABA</t>
   </si>
@@ -656,519 +656,531 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>39593800</v>
+      </c>
+      <c r="E8" s="3">
         <v>35285800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>40724400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>34806600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>34569900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>32585100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>38382000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>33716300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>33471800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>30728300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>36715800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>30807500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>32287100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>30309200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>34928600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>28623400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>28576300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>28175500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>33422700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>28528100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>29548400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>26085400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>30774900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>22849500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>22656700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>17897000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>24861000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>18567800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>17558100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>14222900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>17032300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>11917300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>11610400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>8886000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>12322200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>8180700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>7447800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>5610500</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>7743900</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>4987100</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>24451800</v>
+      </c>
+      <c r="E9" s="3">
         <v>23109000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>24238500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>21179500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>19044200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>20068400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>22266300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>20533000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>20105700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>20510800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>22030200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>19141000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>19627800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>20044500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>21147700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>18128000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>18024900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>19185500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>20206500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>18444000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>17822800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>17463200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>16880500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>13256500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>12455300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>11350900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>12985400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>10225800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>9164800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>8459400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>8831900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>6548200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>6272900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>4663700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>5205900</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>3265300</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>2591200</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>2252700</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>2781500</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1908500</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>15142100</v>
+      </c>
+      <c r="E10" s="3">
         <v>12176800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>16485900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>13627100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>15525700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>12516800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>16115700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>13183300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>13366100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>10217600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>14685600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>11666500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>12659300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>10264700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>13780900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>10495500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>10551300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>8990000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>13216100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>10084100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>11725600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>8622200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>13894400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>9593000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>10201400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>6546100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>11875600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>8342000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8393300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>5763500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>8200400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>5369100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>5337500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>4222300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>7116300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>4915300</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>4856600</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>3357800</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>4962400</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>3078600</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1211,130 +1223,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>3316600</v>
+      </c>
+      <c r="E12" s="3">
         <v>2748400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2213200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2401300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2094000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2058000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2008700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2021800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1840300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1950700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1902200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1948600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1443000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2020600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1906200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2093100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1973100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1511100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2163800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2174500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1941600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1851600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1894100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>2835900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1633000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1657500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1705600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1706400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1600800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1317200</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1292700</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>1170800</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>1651500</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>959300</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>933400</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>754400</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>696900</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>657100</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>642800</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>601200</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1455,252 +1471,261 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>656300</v>
+      </c>
+      <c r="E14" s="3">
         <v>481100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1360400</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="3">
         <v>635400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>845400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-210700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>636200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2845900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3395100</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1093300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-953800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>382600</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>3463900</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>10</v>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>89900</v>
       </c>
-      <c r="AE14" s="3" t="s">
+      <c r="AF14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>10</v>
+      <c r="AH14" s="3">
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
+      <c r="AJ14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
         <v>73300</v>
-      </c>
-      <c r="AL14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AM14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AN14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO14" s="3">
         <v>309000</v>
       </c>
-      <c r="AO14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP14" s="3" t="s">
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>97900</v>
+      </c>
+      <c r="E15" s="3">
         <v>-103400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>120200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>116000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>112600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>-520600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>282500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>235100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>246600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-1768000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>355000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>333200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>341800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-46100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>779600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>377000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>382400</v>
-      </c>
-      <c r="T15" s="3">
-        <v>390900</v>
       </c>
       <c r="U15" s="3">
         <v>390900</v>
       </c>
       <c r="V15" s="3">
+        <v>390900</v>
+      </c>
+      <c r="W15" s="3">
         <v>413100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>441300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>475400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>441500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>425600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>435000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>633100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>503800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>469000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>468400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>487200</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>408000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>365400</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>301900</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>190700</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>305300</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>259400</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>294700</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>190900</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>183400</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>188600</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1740,252 +1765,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>36705600</v>
+      </c>
+      <c r="E17" s="3">
         <v>34927700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>37842100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>34053000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>29685900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>28027000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>31891300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>28691600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>28086500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>26627200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>30639700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>26204800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>26148300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>27516500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>29990000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>25150500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>25108700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>25867200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>32448800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>26395000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>25118100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>27152100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>23953800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>20840400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>17542600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>16780600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>18769500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>15390900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>13834100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>12889600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>13140400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>10027700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>10459700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>7563000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>8464100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>5719400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>4848700</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>4533300</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>4738700</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>3671700</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2888200</v>
+      </c>
+      <c r="E18" s="3">
         <v>358100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2882300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>753600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4884000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4558100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6490700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5024700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5385200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4101100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>6076100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4602700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6138900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2792800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4938700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3472900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3467600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2308300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>973800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2133100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4430200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1066700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>6821100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2009100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>5114100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1116400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>6091400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3177000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3724000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1333300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3891900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1889600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1150700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1323000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>3858100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>2461200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>2599100</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1077200</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>3005200</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>1315400</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2028,231 +2060,235 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-210400</v>
+      </c>
+      <c r="E20" s="3">
         <v>9000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>31200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-452600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-190000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-51500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1057300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>71300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-242500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>33900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>165600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>599300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-581100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-255300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2393600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5458400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>761600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-4845000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3230100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1392100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2335000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>309900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>5966400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1717900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>3482100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1023100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2790600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>10377600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>349600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>3059700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1735100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>714200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>1027700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>405900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>3457200</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>767600</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>498500</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>1326000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>560200</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>187200</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3196500</v>
+      </c>
+      <c r="E21" s="3">
         <v>245700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2971400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1322200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5186600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4089000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7830400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5188500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5874300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2299100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6265500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4336500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7061800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3002000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>7722500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1926100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5542300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2396700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>4157900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>704500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>8197100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>564900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>12940900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>3812200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>9866300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1609300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>8955000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>13596400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>5257300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>4411900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>5740800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2772500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>2890300</v>
-      </c>
-      <c r="AJ21" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AK21" s="3" t="s">
         <v>10</v>
@@ -2263,383 +2299,395 @@
       <c r="AM21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AN21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO21" s="3">
         <v>2424500</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>3570300</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1520600</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>346200</v>
+      </c>
+      <c r="E22" s="3">
         <v>324900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>365600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>353600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>345900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>344000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>340500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>346000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>301100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>301500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>300700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>254100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>246000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>252700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>218500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>191800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>172900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>164200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>163400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>180100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>182000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>161500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>152000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>162200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>165500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>182400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>201600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>212200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>205600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>198200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>193700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>187500</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>174000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>168600</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>125300</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>110900</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>118700</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>98300</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>101900</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>97100</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3421600</v>
+      </c>
+      <c r="E23" s="3">
         <v>4446900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3444300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3674900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7153600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2594500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7889100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7260100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4690400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>919700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2214800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4453200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5380600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3749200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>7113700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2177300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4056200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2700800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4040500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>560900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6583300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-918300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>12635500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3564800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>8430800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-89100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>8680500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>13342400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3867900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>4194900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>5433200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2416300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2004400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1560300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>7190000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>3117900</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>2978900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>2304900</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>3463400</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>1405400</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1884100</v>
+      </c>
+      <c r="E24" s="3">
         <v>1039500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1209500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>779600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1237500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>944500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1527400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1052000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1384800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>792500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>703400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>794500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>830400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>547100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>538500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>355300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>750600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>287100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1316200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>865300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1306400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>981200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1279800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>281600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1639200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>411400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1294500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>439200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1025500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>764400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>811300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>38800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>812800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>597500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>988900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>403500</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>690600</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>662100</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>743100</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>294100</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2760,252 +2808,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1537500</v>
+      </c>
+      <c r="E26" s="3">
         <v>3407400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2234800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2895300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5916100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1650000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>6361600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6208100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3305700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>127300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1511400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3658700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4550300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3202100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>6575200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2532600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3305600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2987900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2724300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-304300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>5276900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1899500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>11355700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3283200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>6791500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-500500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>7386000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>12903300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2842500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3430500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>4621900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2377500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1191600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>962900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>6201200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>2714400</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>2288300</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1642800</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>2720300</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>1111400</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1551200</v>
+      </c>
+      <c r="E27" s="3">
         <v>3693600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2333600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2948400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6018600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1706300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6705600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6254800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3339700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>452900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2035400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3797100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4733900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3423400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>6600000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2840700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3161200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1239700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2814700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>762900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>6483200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-762700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>11056200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>4239400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>7013000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>495000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>8054500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>11317000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3246900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3929300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>4800100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2803800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1246100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1084900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>3572700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>2622100</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>2179100</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1548400</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>2596700</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3126,8 +3183,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3248,8 +3308,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3370,8 +3433,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3492,252 +3558,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>210400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-9000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-31200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>452600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>190000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>51500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1057300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-71300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>242500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-33900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-165600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-599300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>581100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>255300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2393600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5458400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-761600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>4845000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3230100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1392100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2335000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-309900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-5966400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1717900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-3482100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1023100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2790600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-10377600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-349600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-3059700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1735100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-714200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-1027700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-405900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-3457200</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-767600</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-498500</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-1326000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-560200</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-187200</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1562500</v>
+      </c>
+      <c r="E33" s="3">
         <v>3703000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2342300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2952400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5674200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1730700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>6730600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>6277400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3356300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>466000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2052600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3816400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4721500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3442000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>6600000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2840700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3161200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1239700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2814700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>762900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>6483200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-762700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>11056200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>4239400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>7013000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>495000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>8054500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>11317000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3246900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3929300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>4800100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2803800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1246100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1084900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>3572700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>2622100</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>2179100</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1548400</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>2596700</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3858,257 +3933,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1562500</v>
+      </c>
+      <c r="E35" s="3">
         <v>3703000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2342300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2952400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5674200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1730700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>6730600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>6277400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3356300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>466000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2052600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3816400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4721500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3442000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>6600000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2840700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3161200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1239700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2814700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>762900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>6483200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-762700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>11056200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>4239400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>7013000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>495000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>8054500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>11317000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3246900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3929300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>4800100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2803800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1246100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1084900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>3572700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>2622100</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>2179100</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1548400</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>2596700</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4151,8 +4235,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4195,260 +4280,267 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>21039000</v>
+      </c>
+      <c r="E41" s="3">
         <v>19069500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>18325200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>18972500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>25561900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>20049200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>22301900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>26087700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>30159600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>34364000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>35933900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>33401300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>31218400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>28109000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>27526200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>28559200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>24569300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>26221100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>40385100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>38694100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>41909600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>44719700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>43449500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>44430400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>45573600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>51743500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>53981500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>36534000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>32166100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>28899100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>27478100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>23005900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>24089600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>28596900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>31492000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>22075400</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>21540800</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>20903500</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>19486000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>15078800</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>35741200</v>
+      </c>
+      <c r="E42" s="3">
         <v>26863700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>30014900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>33501400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>32565800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>38854700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>39798600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>29338700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>31616900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>44720400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>50712200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>45314800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>43851500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>48242000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>45672400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>38739900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>39836300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>36617000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>27806800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>26581900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>27509400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>22575900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>20883300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>16090800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>11389600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>5121400</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1021700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1066000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1540200</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>2006300</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1653700</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>2402000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>2475900</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1564100</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1771400</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>2413700</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>1108600</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>1027500</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>1135400</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>1065100</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" s="3">
         <v>13644000</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>10</v>
@@ -4456,11 +4548,11 @@
       <c r="G43" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I43" s="3">
         <v>10487000</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>10</v>
@@ -4468,11 +4560,11 @@
       <c r="K43" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M43" s="3">
         <v>9542600</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>10</v>
@@ -4480,12 +4572,12 @@
       <c r="O43" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P43" s="3">
+      <c r="P43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q43" s="3">
         <v>9337900</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -4561,16 +4653,19 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="3">
         <v>2741500</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>10</v>
@@ -4578,11 +4673,11 @@
       <c r="G44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I44" s="3">
         <v>2602800</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>10</v>
@@ -4590,11 +4685,11 @@
       <c r="K44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M44" s="3">
         <v>3526100</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>10</v>
@@ -4602,12 +4697,12 @@
       <c r="O44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P44" s="3">
+      <c r="P44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q44" s="3">
         <v>4155800</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
       <c r="R44" s="3">
         <v>0</v>
       </c>
@@ -4683,618 +4778,636 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6269100</v>
+      </c>
+      <c r="E45" s="3">
         <v>22961700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6054100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5671100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5787300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>18062600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>30766000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6483700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>28177900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>9651500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>27195800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>25161900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>25647900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>9318600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>29487800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>26333200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>25257300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>25330800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>24828600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>25422400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>23522800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>22260200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>18870600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>16538500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>15436500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>15610300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>15742300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>14770600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>10696400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>10208500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>8872000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>7886200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>7438400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>6692600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>6553500</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>5882700</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>5013300</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>4517500</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>3887600</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>3682000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>106709200</v>
+      </c>
+      <c r="E46" s="3">
         <v>88550600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>87529500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>90827500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>95769100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>92889000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>92866500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>86834700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>89954500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>104267600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>113842000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>103878000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>100717700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>101608000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>102686400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>93632300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>89662900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>88168900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>93020500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>90698400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>92941800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>89555700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>83203500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>77059700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>72399700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>72475200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>70745500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>52370500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>44402800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>41113900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>38003800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>33294100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>34003900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>36853600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>39816900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>30371800</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>27662700</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>26448500</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>24509000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>19825900</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>80412300</v>
+      </c>
+      <c r="E47" s="3">
         <v>95216300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>92819400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>86922000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>79733100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>78135100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>76295000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>78010700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>73595100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>58731800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>60528800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>62509800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>62278200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>65963600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>61483200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>57773100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>62111600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>61204400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>65630300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>65584300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>65281500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>60887500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>59266900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>58735200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>55079600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>54946500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>55746500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>51631700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>38852700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>36743700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>33087900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>30691800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>28385900</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>25523900</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>24392700</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>23730600</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>22240600</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>22079200</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>22453800</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>22895300</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>46004200</v>
+      </c>
+      <c r="E48" s="3">
         <v>47586500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>36383100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>34630200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>30826500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>33425200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>31076600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>29641000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>26726900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>36297800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>25611400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>24591700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>24248700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>36897900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>25065700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>24809000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>24719400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>34500500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>22741400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>22326900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>21917300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20519800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>20473800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>17393900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>16424900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>21612600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>19466200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>19627200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>18193700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>13999600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>13188900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>12180000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>11286000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>9539800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>9642600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>7359200</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>6518500</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>2938600</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>2893900</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>2385100</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>38151600</v>
+      </c>
+      <c r="E49" s="3">
         <v>38327600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>37753100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>38625100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>38485600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>38091600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>37896700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>40277600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>39218100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>39696600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>40598100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>42253200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>42902800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>45857500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>44701000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>44964000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>45496200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>45402400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>45628900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>51142200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>51691900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>50613700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>51132800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>49004600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>49288400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>52874900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>52626800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>53469800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>50862400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>50688100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>45348800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>35607600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>37195600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>27205800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>28168500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>21480600</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>21635700</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>20291600</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>19700100</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>19685800</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5415,8 +5528,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5537,130 +5653,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>17574000</v>
+      </c>
+      <c r="E52" s="3">
         <v>5149000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>14058200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>13614900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>13021600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4281400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>16001200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>16531500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>16147200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3852100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>16222900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>15045900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>14851300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2621000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>15897800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>15426700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>15507100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4845800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>15549900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>15552800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>14506300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>13701700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>13552100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>9065700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>8569300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3651800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>4590900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3806500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>3348900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>4262100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>3683500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>3660800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>3433600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>3769800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>3562900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>2961100</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>2635200</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1947900</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1829800</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>1582400</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5781,130 +5903,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>288851300</v>
+      </c>
+      <c r="E54" s="3">
         <v>276853600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>268543300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>264619600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>257835900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>248636000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>254136000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>251295500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>245641700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>244419200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>256803200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>248278700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>244998700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>255203500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>249834000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>236605100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>237497300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>234122000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>242570900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>245304600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>246338700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>235278300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>227629000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>211259100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>201761900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>205560900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>203175800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>180905600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>155660500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>146807400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>133312900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>115434400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>114305100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>102893000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>105583600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>85903300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>80692600</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>73705700</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>71386600</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>66374500</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5947,8 +6075,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5991,16 +6120,17 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57" s="3">
         <v>20107600</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>10</v>
@@ -6008,11 +6138,11 @@
       <c r="G57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I57" s="3">
         <v>16401400</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>10</v>
@@ -6020,11 +6150,11 @@
       <c r="K57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M57" s="3">
         <v>17666400</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>10</v>
@@ -6032,48 +6162,48 @@
       <c r="O57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P57" s="3">
+      <c r="P57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q57" s="3">
         <v>16559700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>41401000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>37560600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>36918600</v>
       </c>
-      <c r="T57" s="3" t="s">
+      <c r="U57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>38835600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>37802900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>35961600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>36321300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>31307500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>26279700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>24271800</v>
       </c>
-      <c r="AB57" s="3" t="s">
+      <c r="AC57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC57" s="3">
-        <v>0</v>
-      </c>
       <c r="AD57" s="3">
         <v>0</v>
       </c>
@@ -6113,504 +6243,519 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4506800</v>
+      </c>
+      <c r="E58" s="3">
         <v>4718000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3525000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3692500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3431700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3652700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2939100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4665200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4115900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4829600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3716600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1122000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1135600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2610600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1630400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1602900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1883600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1220800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1089300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2679000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2443400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1870400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2094500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>722500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>669500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>806900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>649000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3768400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3516800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3417500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3313000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1262700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1964700</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>864900</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>956800</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>2428100</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>2442100</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>2166500</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1989300</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>802800</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>13083900</v>
+      </c>
+      <c r="E59" s="3">
         <v>38532500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11990000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10827100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10807000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>34517600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>13093100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12745200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12894200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>30677900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>15112000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13022400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>12775500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>31687700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>15874900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>13732600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>13411500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>51772100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>16634700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>14652800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>14475700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>14336500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>16453900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>11744900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>11617700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>37060600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>39764300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>34290100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>28673900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>28173100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>27007000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>22264000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>21594200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>18621100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>19292000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>15311900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>13438700</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>11440500</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>11476900</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>9003700</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>78356100</v>
+      </c>
+      <c r="E60" s="3">
         <v>69069200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>65739900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>62385800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>66113900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>59993900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>62659600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>63421200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>63698400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>58376400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>63285900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>53423500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>52430100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>56098400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>58906400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>52896100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>52213700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>52992900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>56559700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>55134700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>52880700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>52528200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>49855900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>38747100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>36559000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>37867500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>40413300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>38058500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>32190700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>31590600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>30320000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>23526700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>23558800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>19486000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>20248800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>17740000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>15880800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>13607000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>13466200</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>9806500</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>34730300</v>
+      </c>
+      <c r="E61" s="3">
         <v>36126700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>37440500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>38861100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>31921900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>30538700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>33271000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>28640800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>28927300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>23646800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>24277700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>26076700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>25934500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>25859800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>20901700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>20701600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>19249000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>18296000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>18149900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>18892700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>19187500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>18891700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>14289200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>17224200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>17814900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>18830400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>18196100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>18958600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>17779000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>17012200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>16446000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>18082000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>17848900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>17149400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>18237200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>11186100</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>11407200</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>11174100</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>11219300</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>12008900</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3921100</v>
+      </c>
+      <c r="E62" s="3">
         <v>982500</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>10</v>
@@ -6618,11 +6763,11 @@
       <c r="G62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I62" s="3">
         <v>576200</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>10</v>
@@ -6630,11 +6775,11 @@
       <c r="K62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M62" s="3">
         <v>401600</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>10</v>
@@ -6642,89 +6787,92 @@
       <c r="O62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q62" s="3">
         <v>266600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>13568800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>13453100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>13622800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>13403800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>13526600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>13729800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>13614700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>13016600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>12820300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>10694800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>10566900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>11144900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>11048800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>10354200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>7139000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>4589600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>4043600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>3657000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>4636800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>3206800</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>3288800</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>2362400</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>2291500</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>1787600</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>1681900</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>1937700</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6845,8 +6993,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6967,8 +7118,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7089,130 +7243,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>124869700</v>
+      </c>
+      <c r="E66" s="3">
         <v>113564500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>110427100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>108452500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>105218700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>98411200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>104145600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>100482400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>100688600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>90330300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>95691100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>87923700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>86836300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>91731600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>112244000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>105638100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>103587700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>103156000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>106870400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>106961600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>105035900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>103575200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>96014900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>83728500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>81439100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>85870200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>87396600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>85691900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>74973700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>70887900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>65336800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>55593000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>57452000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>49974200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>53203800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>37956500</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>36261200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>32724800</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>32523100</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>29976500</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7255,8 +7415,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7377,8 +7538,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7499,8 +7663,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7556,73 +7723,76 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
         <v>1461600</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>1477500</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>1201100</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>1207300</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>1175300</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>1183700</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>1152400</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>1425200</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>1200300</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>1171000</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>1083400</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>1037300</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>1040600</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AI70" s="3">
         <v>839900</v>
       </c>
-      <c r="AI70" s="3">
+      <c r="AJ70" s="3">
         <v>452700</v>
       </c>
-      <c r="AJ70" s="3">
+      <c r="AK70" s="3">
         <v>430600</v>
       </c>
-      <c r="AK70" s="3">
+      <c r="AL70" s="3">
         <v>442100</v>
       </c>
-      <c r="AL70" s="3">
+      <c r="AM70" s="3">
         <v>133300</v>
       </c>
-      <c r="AM70" s="3">
+      <c r="AN70" s="3">
         <v>113200</v>
       </c>
-      <c r="AN70" s="3">
+      <c r="AO70" s="3">
         <v>435100</v>
       </c>
-      <c r="AO70" s="3">
+      <c r="AP70" s="3">
         <v>515800</v>
       </c>
-      <c r="AP70" s="3">
+      <c r="AQ70" s="3">
         <v>561800</v>
       </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7743,130 +7913,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>105807500</v>
+      </c>
+      <c r="E72" s="3">
         <v>105113500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>100002600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>95947600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>92618300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>91147800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>89370200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>86891000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>79785900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>84845900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>89068500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>89093400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>86996400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>89094100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>84254400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>76966400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>80286100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>79174500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>81449200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>82138400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>86310300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>78268100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>79111700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>72029000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>67773800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>64563300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>63003500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>55694500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>43446200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>39985800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>34455500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>29692900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>27742100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>25305600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>25027300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>21444900</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>18812900</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>16290200</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>14732300</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>12126100</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7987,8 +8163,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8109,8 +8288,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8231,130 +8413,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>154433800</v>
+      </c>
+      <c r="E76" s="3">
         <v>153809600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>148641100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>145029600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>141499200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>139166000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>137157900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>135993300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>129081900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>136631000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>142519300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>141858100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>139749300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>144071700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>137590000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>130967000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>133909600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>130966000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>134238900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>136865400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>140101700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>130495800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>130438900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>126346900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>119170500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>118265600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>114579000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>94042700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>79603400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>74882100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>66935500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>59001500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>56400400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>52488100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>51937700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>47813500</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>44318200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>40545700</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>38347700</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>35836300</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8475,257 +8663,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1562500</v>
+      </c>
+      <c r="E81" s="3">
         <v>3703000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2342300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2952400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5674200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1730700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>6730600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>6277400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3356300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>466000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2052600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3816400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4721500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3442000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>6600000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2840700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3161200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1239700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2814700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>762900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>6483200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-762700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>11056200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>4239400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>7013000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>495000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>8054500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>11317000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3246900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3929300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>4800100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2803800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1246100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1084900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>3572700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>2622100</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>2179100</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1548400</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>2596700</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>1108600</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8768,53 +8965,54 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>961900</v>
+      </c>
+      <c r="E83" s="3">
         <v>1263300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>986600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>964600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>843000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>947000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>949000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>876000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>921200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>996200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1031400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1004600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>999400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1192800</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
@@ -8890,8 +9088,11 @@
       <c r="AP83" s="3">
         <v>0</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9012,8 +9213,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9134,8 +9338,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9256,8 +9463,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9378,8 +9588,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9500,130 +9713,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3377800</v>
+      </c>
+      <c r="E89" s="3">
         <v>1364300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5151500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1418600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2885600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3792500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>9715600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4481900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4628700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3232500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>9126600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>6747100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6247100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4571300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>12317400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>6509000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4708500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-972100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>11072800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>5093200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>4826100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>3366300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>14366600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>8001100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>7382600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>338800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>14859800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>7383300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>5288000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2822300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>9425100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>4395700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>5182100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>2063700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>8226100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>4470300</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>3839800</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1562800</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>5441400</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>2502300</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9666,40 +9885,41 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9963200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-18276900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4146000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4424800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5398800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-11847600</v>
       </c>
-      <c r="I91" s="3" t="s">
+      <c r="J91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4217700</v>
       </c>
-      <c r="K91" s="3" t="s">
+      <c r="L91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4443900</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>10</v>
@@ -9707,89 +9927,92 @@
       <c r="O91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P91" s="3">
+      <c r="P91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-4997700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-6897000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-12112000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-11843000</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-18710000</v>
       </c>
       <c r="U91" s="3">
         <v>-18710000</v>
       </c>
       <c r="V91" s="3">
+        <v>-18710000</v>
+      </c>
+      <c r="W91" s="3">
         <v>-5844000</v>
       </c>
-      <c r="W91" s="3" t="s">
+      <c r="X91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-453500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-813500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2757100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2009700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-281000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1025400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1533000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-975000</v>
       </c>
-      <c r="AF91" s="3" t="s">
+      <c r="AG91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1466800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1734700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1607700</v>
       </c>
-      <c r="AJ91" s="3" t="s">
+      <c r="AK91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-1546700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-1287200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-532600</v>
       </c>
-      <c r="AN91" s="3">
-        <v>0</v>
-      </c>
       <c r="AO91" s="3">
         <v>0</v>
       </c>
       <c r="AP91" s="3">
         <v>0</v>
       </c>
+      <c r="AQ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9910,8 +10133,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10032,130 +10258,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2791800</v>
+      </c>
+      <c r="E94" s="3">
         <v>1406900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3676700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-9783700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>2558400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5449900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-15207800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>137400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4930400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>2806900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4361200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3256400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1736700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3902600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-10283500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1125700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3837900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-12048000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4655600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4232200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-6861400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3856000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-11095900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-10175700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-9980400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-5165700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5017900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3331300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-3229200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2548200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-4510100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-4420500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-10283200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-2866200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-3607000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-3795100</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-2064700</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-441400</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-1184700</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-831100</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10198,40 +10430,41 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="3">
         <v>6100</v>
       </c>
-      <c r="E96" s="3" t="s">
+      <c r="F96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>4722600</v>
       </c>
-      <c r="G96" s="3" t="s">
+      <c r="H96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>4007000</v>
       </c>
-      <c r="I96" s="3" t="s">
+      <c r="J96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>4137400</v>
       </c>
-      <c r="K96" s="3" t="s">
+      <c r="L96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>2485400</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>10</v>
@@ -10242,8 +10475,8 @@
       <c r="P96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10320,8 +10553,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10442,8 +10678,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10564,8 +10803,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10686,370 +10928,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1394000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2175000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1964700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1531400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-381200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-565300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1952400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-9520600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2694700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-7480400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2427600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1697000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3397000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1356600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3356500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1584700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2922500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1465600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2576100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-3364700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1647000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>4213600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-791400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1489200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-679200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>464500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>9437000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>328600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>686400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>109400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1294700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-486600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>614200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-660700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>5086600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-61700</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-1320000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>361000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-103300</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>1429600</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-133700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-78400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>456400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-350100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>90700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>263100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-372700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>111400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>595500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-174800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-294600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>483100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>496500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-144000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-286300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>474700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>462400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-126100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-816200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>27700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-314800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>159900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-575200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-567800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-51700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>363500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-300600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>367100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>210400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-173700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-9600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>233700</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>399300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-380700</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-224000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-120400</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-162100</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-64900</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>253800</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1756400</v>
+      </c>
+      <c r="E102" s="3">
         <v>442100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-704000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-6901900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>4929100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2301100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3083400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5251400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2905800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1177900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1965100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1905100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>5182400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-862800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1608900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4273300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1589600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-14611800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>3025000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2476000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3997200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3883800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1904100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1253100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-3328700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-3998900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>18978300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>4747700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>2955700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>209800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>3610700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-277700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-4087600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1843900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>9481900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>494500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>291500</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>1417500</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>4407300</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>3117700</v>
       </c>
     </row>
